--- a/static/results/2026_po.xlsx
+++ b/static/results/2026_po.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
   <si>
     <t xml:space="preserve">Codice_meccanografico</t>
   </si>
@@ -58,21 +58,81 @@
     <t xml:space="preserve">Sezione</t>
   </si>
   <si>
+    <t xml:space="preserve">MIPS08000T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liceo Scientifico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Volta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lombardia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pietro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-11-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea Edoardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbieri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPS01000P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statale "A. Di Savoia"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistoia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toscana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giovanni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasselli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-02-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
     <t xml:space="preserve">TNPS01000V</t>
   </si>
   <si>
-    <t xml:space="preserve">Liceo Scientifico</t>
-  </si>
-  <si>
     <t xml:space="preserve">Galileo Galilei</t>
   </si>
   <si>
     <t xml:space="preserve">Trento</t>
   </si>
   <si>
-    <t xml:space="preserve">TN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trentino-Alto Adige</t>
   </si>
   <si>
@@ -91,6 +151,102 @@
     <t xml:space="preserve">Asa</t>
   </si>
   <si>
+    <t xml:space="preserve">Matteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cappiello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBPS240002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banfi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vimercate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monza e della Brianza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bamber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-03-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VTPS010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Ruffini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viterbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celentano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-01-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-12-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDIS01600T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istituto Istruzione Superiore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Malignani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Udine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friuli-Venezia Giulia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pividori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lsm A</t>
+  </si>
+  <si>
     <t xml:space="preserve">TNPC02000A</t>
   </si>
   <si>
@@ -109,57 +265,30 @@
     <t xml:space="preserve">Di Leo</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
     <t xml:space="preserve">2008-10-10</t>
   </si>
   <si>
-    <t xml:space="preserve">PTPS01000P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statale "A. Di Savoia"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pistoia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toscana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giovanni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasselli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-02-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
+    <t xml:space="preserve">Marco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-06-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
   </si>
   <si>
     <t xml:space="preserve">UDIS01300A</t>
   </si>
   <si>
-    <t xml:space="preserve">Istituto Istruzione Superiore</t>
-  </si>
-  <si>
     <t xml:space="preserve">Della Bassa Friulana</t>
   </si>
   <si>
     <t xml:space="preserve">Cervignano del Friuli</t>
   </si>
   <si>
-    <t xml:space="preserve">UD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friuli-Venezia Giulia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Diego</t>
   </si>
   <si>
@@ -172,19 +301,25 @@
     <t xml:space="preserve">Tela</t>
   </si>
   <si>
-    <t xml:space="preserve">MIPS08000T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. Volta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lombardia</t>
+    <t xml:space="preserve">TVPS01000X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liceo Da Vinci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treviso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veneto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-02-25</t>
   </si>
   <si>
     <t xml:space="preserve">Maiellaro</t>
@@ -193,51 +328,6 @@
     <t xml:space="preserve">2008-02-14</t>
   </si>
   <si>
-    <t xml:space="preserve">MBPS240002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banfi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vimercate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bamber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009-03-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TVPS01000X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liceo Da Vinci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veneto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008-02-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">RMIS077005</t>
   </si>
   <si>
@@ -247,112 +337,13 @@
     <t xml:space="preserve">Zagarolo</t>
   </si>
   <si>
-    <t xml:space="preserve">RM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lazio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marco</t>
+    <t xml:space="preserve">Roma</t>
   </si>
   <si>
     <t xml:space="preserve">D'Amico</t>
   </si>
   <si>
     <t xml:space="preserve">2008-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VTPS010006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paolo Ruffini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viterbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celentano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009-01-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matteo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cappiello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UDIS01600T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. Malignani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Udine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miriam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pividori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008-12-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lsm A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Edoardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbieri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2009-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pietro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Picchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-11-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008-12-29</t>
   </si>
 </sst>
 </file>
@@ -363,7 +354,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -384,6 +375,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -428,8 +426,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -454,8 +456,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.32"/>
@@ -471,41 +473,41 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.91"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -523,560 +525,598 @@
         <v>15</v>
       </c>
       <c r="E2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="G2" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="H2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="I2" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="I3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="K3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="0" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>2</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="J5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="K5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>56</v>
+        <v>19</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>19</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>79</v>
+        <v>19</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>4</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>4</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>90</v>
+        <v>40</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>96</v>
+        <v>19</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="F13" s="0" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>103</v>
+        <v>19</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>110</v>
+        <v>19</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>107</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/static/results/2026_po.xlsx
+++ b/static/results/2026_po.xlsx
@@ -457,7 +457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.32"/>
